--- a/src/data/calibration_data_white.xlsx
+++ b/src/data/calibration_data_white.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew Tan\Documents\ECSE211\ECSE211_W26_Final_Project\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0CA3B2FB-9BD4-47B8-8D11-7455E8C958AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFB8778-1354-4CC4-9134-F47B31522EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DE9263B8-45A1-450F-808E-F27ED0380E00}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration_data_white" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>R</t>
   </si>
@@ -31,10 +44,16 @@
     <t>B</t>
   </si>
   <si>
-    <t>avg</t>
+    <t>vector avg</t>
   </si>
   <si>
-    <t>std dev</t>
+    <t>vector std dev</t>
+  </si>
+  <si>
+    <t>ratio avg</t>
+  </si>
+  <si>
+    <t>ratio std dev</t>
   </si>
 </sst>
 </file>
@@ -42,7 +61,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="186" formatCode="0.000000000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000000000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -523,7 +542,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -899,13 +918,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79FD8BBB-CFE1-42B5-9C38-5EE10FCBE74A}">
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="10" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -916,7 +935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>93</v>
       </c>
@@ -938,23 +957,35 @@
         <f t="shared" si="0"/>
         <v>3.7970062066447607E-3</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2">
+        <f>A2/($A2+$B2+$C2)</f>
+        <v>0.27433628318584069</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2:K2" si="1">B2/($A2+$B2+$C2)</f>
+        <v>0.26548672566371684</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="1"/>
+        <v>0.46017699115044247</v>
+      </c>
+      <c r="M2" t="s">
         <v>3</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <f>AVERAGE(E2:E90)</f>
         <v>2.3003182222495313E-3</v>
       </c>
-      <c r="K2">
-        <f t="shared" ref="K2:L2" si="1">AVERAGE(F2:F90)</f>
+      <c r="O2">
+        <f>AVERAGE(F2:F90)</f>
         <v>2.1931821218544563E-3</v>
       </c>
-      <c r="L2">
-        <f t="shared" si="1"/>
+      <c r="P2">
+        <f>AVERAGE(G2:G90)</f>
         <v>3.8588418761569517E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>93</v>
       </c>
@@ -976,23 +1007,35 @@
         <f t="shared" ref="G3:G66" si="4">C3/($A3^2 + $B3^2 + $C3^2)</f>
         <v>3.8440279382945582E-3</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="5">A3/($A3+$B3+$C3)</f>
+        <v>0.27844311377245506</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="6">B3/($A3+$B3+$C3)</f>
+        <v>0.26347305389221559</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="7">C3/($A3+$B3+$C3)</f>
+        <v>0.45808383233532934</v>
+      </c>
+      <c r="M3" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="1">
+      <c r="N3" s="1">
         <f>_xlfn.STDEV.P(E2:E90)</f>
         <v>8.5778549410512247E-5</v>
       </c>
-      <c r="K3" s="1">
-        <f t="shared" ref="K3:L3" si="5">_xlfn.STDEV.P(F2:F90)</f>
+      <c r="O3" s="1">
+        <f>_xlfn.STDEV.P(F2:F90)</f>
         <v>7.7360638379908009E-5</v>
       </c>
-      <c r="L3" s="1">
-        <f t="shared" si="5"/>
+      <c r="P3" s="1">
+        <f>_xlfn.STDEV.P(G2:G90)</f>
         <v>1.4755355263543251E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>90</v>
       </c>
@@ -1014,8 +1057,20 @@
         <f t="shared" si="4"/>
         <v>3.9202537848502823E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <f t="shared" si="5"/>
+        <v>0.2735562310030395</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="6"/>
+        <v>0.26443768996960487</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="7"/>
+        <v>0.46200607902735563</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>95</v>
       </c>
@@ -1037,8 +1092,35 @@
         <f t="shared" si="4"/>
         <v>3.8080541589924836E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <f t="shared" si="5"/>
+        <v>0.28273809523809523</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="6"/>
+        <v>0.26190476190476192</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="7"/>
+        <v>0.45535714285714285</v>
+      </c>
+      <c r="M5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>AVERAGE(I2:I90)</f>
+        <v>0.27541112500332809</v>
+      </c>
+      <c r="O5">
+        <f t="shared" ref="O5:P5" si="8">AVERAGE(J2:J90)</f>
+        <v>0.26260195967526678</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="8"/>
+        <v>0.46198691532140507</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>93</v>
       </c>
@@ -1060,8 +1142,35 @@
         <f t="shared" si="4"/>
         <v>3.8057580625231683E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <f t="shared" si="5"/>
+        <v>0.27596439169139464</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="6"/>
+        <v>0.26706231454005935</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="7"/>
+        <v>0.45697329376854601</v>
+      </c>
+      <c r="M6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.STDEV.P(I2:I90)</f>
+        <v>2.2412874593234172E-3</v>
+      </c>
+      <c r="O6">
+        <f t="shared" ref="O6:P6" si="9">_xlfn.STDEV.P(J2:J90)</f>
+        <v>2.0033234018412317E-3</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="9"/>
+        <v>2.7673359840225888E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>93</v>
       </c>
@@ -1083,8 +1192,20 @@
         <f t="shared" si="4"/>
         <v>3.8014420954529849E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <f t="shared" si="5"/>
+        <v>0.27514792899408286</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="6"/>
+        <v>0.26627218934911245</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="7"/>
+        <v>0.45857988165680474</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>91</v>
       </c>
@@ -1106,8 +1227,20 @@
         <f t="shared" si="4"/>
         <v>3.8845868792966851E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <f t="shared" si="5"/>
+        <v>0.27492447129909364</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="6"/>
+        <v>0.26586102719033233</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="7"/>
+        <v>0.45921450151057402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>90</v>
       </c>
@@ -1129,8 +1262,20 @@
         <f t="shared" si="4"/>
         <v>3.9326564708906308E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <f t="shared" si="5"/>
+        <v>0.2735562310030395</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="6"/>
+        <v>0.26139817629179329</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="7"/>
+        <v>0.46504559270516715</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>93</v>
       </c>
@@ -1152,8 +1297,20 @@
         <f t="shared" si="4"/>
         <v>3.8182042123414213E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <f t="shared" si="5"/>
+        <v>0.27596439169139464</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="6"/>
+        <v>0.26409495548961426</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="7"/>
+        <v>0.4599406528189911</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>91</v>
       </c>
@@ -1175,8 +1332,20 @@
         <f t="shared" si="4"/>
         <v>3.9316458948991393E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <f t="shared" si="5"/>
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="6"/>
+        <v>0.25835866261398177</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="7"/>
+        <v>0.46504559270516715</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>92</v>
       </c>
@@ -1198,8 +1367,20 @@
         <f t="shared" si="4"/>
         <v>3.857328924957419E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <f t="shared" si="5"/>
+        <v>0.27544910179640719</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="6"/>
+        <v>0.26347305389221559</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="7"/>
+        <v>0.46107784431137727</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>91</v>
       </c>
@@ -1221,8 +1402,20 @@
         <f t="shared" si="4"/>
         <v>3.919445089090018E-3</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="6"/>
+        <v>0.26139817629179329</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="7"/>
+        <v>0.46200607902735563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>91</v>
       </c>
@@ -1244,8 +1437,20 @@
         <f t="shared" si="4"/>
         <v>3.9243203908727068E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <f t="shared" si="5"/>
+        <v>0.27743902439024393</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="6"/>
+        <v>0.26219512195121952</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="7"/>
+        <v>0.46036585365853661</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>90</v>
       </c>
@@ -1267,8 +1472,20 @@
         <f t="shared" si="4"/>
         <v>3.9152464302164899E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="6"/>
+        <v>0.26363636363636361</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="7"/>
+        <v>0.46363636363636362</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>93</v>
       </c>
@@ -1290,8 +1507,20 @@
         <f t="shared" si="4"/>
         <v>3.8440279382945582E-3</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <f t="shared" si="5"/>
+        <v>0.27844311377245506</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="6"/>
+        <v>0.26347305389221559</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="7"/>
+        <v>0.45808383233532934</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>92</v>
       </c>
@@ -1313,8 +1542,20 @@
         <f t="shared" si="4"/>
         <v>3.857328924957419E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <f t="shared" si="5"/>
+        <v>0.27544910179640719</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="6"/>
+        <v>0.26347305389221559</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="7"/>
+        <v>0.46107784431137727</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>91</v>
       </c>
@@ -1336,8 +1577,20 @@
         <f t="shared" si="4"/>
         <v>3.919445089090018E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <f t="shared" si="5"/>
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="6"/>
+        <v>0.26139817629179329</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="7"/>
+        <v>0.46200607902735563</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>93</v>
       </c>
@@ -1359,8 +1612,20 @@
         <f t="shared" si="4"/>
         <v>3.8270091798194052E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <f t="shared" si="5"/>
+        <v>0.27761194029850744</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="6"/>
+        <v>0.2656716417910448</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="7"/>
+        <v>0.45671641791044776</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>91</v>
       </c>
@@ -1382,8 +1647,20 @@
         <f t="shared" si="4"/>
         <v>3.8701622971285894E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <f t="shared" si="5"/>
+        <v>0.27245508982035926</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="6"/>
+        <v>0.26347305389221559</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="7"/>
+        <v>0.46407185628742514</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>92</v>
       </c>
@@ -1405,8 +1682,20 @@
         <f t="shared" si="4"/>
         <v>3.8837928303140251E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <f t="shared" si="5"/>
+        <v>0.27794561933534745</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="6"/>
+        <v>0.26283987915407853</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="7"/>
+        <v>0.45921450151057402</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>92</v>
       </c>
@@ -1428,8 +1717,20 @@
         <f t="shared" si="4"/>
         <v>3.9057448074286748E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f t="shared" si="5"/>
+        <v>0.2796352583586626</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="6"/>
+        <v>0.26139817629179329</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="7"/>
+        <v>0.45896656534954405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>92</v>
       </c>
@@ -1451,8 +1752,20 @@
         <f t="shared" si="4"/>
         <v>3.857328924957419E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" si="5"/>
+        <v>0.27544910179640719</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="6"/>
+        <v>0.26347305389221559</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="7"/>
+        <v>0.46107784431137727</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>91</v>
       </c>
@@ -1474,8 +1787,20 @@
         <f t="shared" si="4"/>
         <v>3.9144450698459805E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <f t="shared" si="5"/>
+        <v>0.27575757575757576</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="6"/>
+        <v>0.26060606060606062</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="7"/>
+        <v>0.46363636363636362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>92</v>
       </c>
@@ -1497,8 +1822,20 @@
         <f t="shared" si="4"/>
         <v>3.8619784435974455E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <f t="shared" si="5"/>
+        <v>0.27627627627627627</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="6"/>
+        <v>0.26426426426426425</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="7"/>
+        <v>0.45945945945945948</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>91</v>
       </c>
@@ -1520,8 +1857,20 @@
         <f t="shared" si="4"/>
         <v>3.8845868792966851E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <f t="shared" si="5"/>
+        <v>0.27492447129909364</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="6"/>
+        <v>0.26586102719033233</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="7"/>
+        <v>0.45921450151057402</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>91</v>
       </c>
@@ -1543,8 +1892,20 @@
         <f t="shared" si="4"/>
         <v>3.9067553232775346E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <f t="shared" si="5"/>
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="6"/>
+        <v>0.26443768996960487</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="7"/>
+        <v>0.45896656534954405</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>93</v>
       </c>
@@ -1566,8 +1927,20 @@
         <f t="shared" si="4"/>
         <v>3.8182042123414213E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <f t="shared" si="5"/>
+        <v>0.27596439169139464</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="6"/>
+        <v>0.26409495548961426</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="7"/>
+        <v>0.4599406528189911</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>93</v>
       </c>
@@ -1589,8 +1962,20 @@
         <f t="shared" si="4"/>
         <v>3.8563629989482647E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <f t="shared" si="5"/>
+        <v>0.27844311377245506</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="6"/>
+        <v>0.26047904191616766</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="7"/>
+        <v>0.46107784431137727</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>91</v>
       </c>
@@ -1612,8 +1997,20 @@
         <f t="shared" si="4"/>
         <v>3.8701622971285894E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <f t="shared" si="5"/>
+        <v>0.27245508982035926</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="6"/>
+        <v>0.26347305389221559</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="7"/>
+        <v>0.46407185628742514</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>93</v>
       </c>
@@ -1635,8 +2032,20 @@
         <f t="shared" si="4"/>
         <v>3.8270091798194052E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <f t="shared" si="5"/>
+        <v>0.27761194029850744</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="6"/>
+        <v>0.2656716417910448</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="7"/>
+        <v>0.45671641791044776</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>90</v>
       </c>
@@ -1658,8 +2067,20 @@
         <f t="shared" si="4"/>
         <v>3.96055185437759E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <f t="shared" si="5"/>
+        <v>0.27607361963190186</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="6"/>
+        <v>0.2607361963190184</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="7"/>
+        <v>0.46319018404907975</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>90</v>
       </c>
@@ -1681,8 +2102,20 @@
         <f t="shared" si="4"/>
         <v>4.0166129296682878E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <f t="shared" si="5"/>
+        <v>0.28125</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="6"/>
+        <v>0.25937500000000002</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="7"/>
+        <v>0.45937499999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>89</v>
       </c>
@@ -1704,8 +2137,20 @@
         <f t="shared" si="4"/>
         <v>3.976249966416808E-3</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <f t="shared" si="5"/>
+        <v>0.27554179566563469</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="6"/>
+        <v>0.26625386996904027</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="7"/>
+        <v>0.45820433436532509</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>89</v>
       </c>
@@ -1727,8 +2172,20 @@
         <f t="shared" si="4"/>
         <v>3.9613830736135161E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <f t="shared" si="5"/>
+        <v>0.27300613496932513</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="6"/>
+        <v>0.26380368098159507</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="7"/>
+        <v>0.46319018404907975</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>88</v>
       </c>
@@ -1750,8 +2207,20 @@
         <f t="shared" si="4"/>
         <v>3.985122210414453E-3</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <f t="shared" si="5"/>
+        <v>0.27160493827160492</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="6"/>
+        <v>0.26543209876543211</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="7"/>
+        <v>0.46296296296296297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>89</v>
       </c>
@@ -1773,8 +2242,20 @@
         <f t="shared" si="4"/>
         <v>4.0024548389679003E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <f t="shared" si="5"/>
+        <v>0.27554179566563469</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="6"/>
+        <v>0.26006191950464397</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="7"/>
+        <v>0.46439628482972134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>87</v>
       </c>
@@ -1796,8 +2277,20 @@
         <f t="shared" si="4"/>
         <v>4.0404040404040404E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <f t="shared" si="5"/>
+        <v>0.27102803738317754</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="6"/>
+        <v>0.26168224299065418</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="7"/>
+        <v>0.46728971962616822</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>87</v>
       </c>
@@ -1819,8 +2312,20 @@
         <f t="shared" si="4"/>
         <v>4.0757479136052351E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <f t="shared" si="5"/>
+        <v>0.27444794952681389</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="6"/>
+        <v>0.26182965299684541</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="7"/>
+        <v>0.4637223974763407</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>89</v>
       </c>
@@ -1842,8 +2347,20 @@
         <f t="shared" si="4"/>
         <v>4.0077465167572216E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <f t="shared" si="5"/>
+        <v>0.27639751552795033</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="6"/>
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="7"/>
+        <v>0.46273291925465837</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>87</v>
       </c>
@@ -1865,8 +2382,20 @@
         <f t="shared" si="4"/>
         <v>4.0944794161885132E-3</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <f t="shared" si="5"/>
+        <v>0.27531645569620256</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="6"/>
+        <v>0.25949367088607594</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="7"/>
+        <v>0.4651898734177215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>86</v>
       </c>
@@ -1888,8 +2417,20 @@
         <f t="shared" si="4"/>
         <v>4.0953919875188058E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <f t="shared" si="5"/>
+        <v>0.27215189873417722</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="6"/>
+        <v>0.26265822784810128</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="7"/>
+        <v>0.4651898734177215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>90</v>
       </c>
@@ -1911,8 +2452,20 @@
         <f t="shared" si="4"/>
         <v>3.9428675875394937E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <f t="shared" si="5"/>
+        <v>0.27522935779816515</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="6"/>
+        <v>0.26299694189602446</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="7"/>
+        <v>0.46177370030581039</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>88</v>
       </c>
@@ -1934,8 +2487,20 @@
         <f t="shared" si="4"/>
         <v>4.0800357701766153E-3</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <f t="shared" si="5"/>
+        <v>0.27848101265822783</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="6"/>
+        <v>0.25949367088607594</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="7"/>
+        <v>0.46202531645569622</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>88</v>
       </c>
@@ -1957,8 +2522,20 @@
         <f t="shared" si="4"/>
         <v>4.0086090933548557E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <f t="shared" si="5"/>
+        <v>0.27329192546583853</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="6"/>
+        <v>0.2639751552795031</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="7"/>
+        <v>0.46273291925465837</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>88</v>
       </c>
@@ -1980,8 +2557,20 @@
         <f t="shared" si="4"/>
         <v>4.0451756529293588E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <f t="shared" si="5"/>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="6"/>
+        <v>0.25937500000000002</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="7"/>
+        <v>0.46562500000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>88</v>
       </c>
@@ -2003,8 +2592,20 @@
         <f t="shared" si="4"/>
         <v>4.0506883433232069E-3</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <f t="shared" si="5"/>
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="6"/>
+        <v>0.2601880877742947</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="7"/>
+        <v>0.46394984326018807</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>87</v>
       </c>
@@ -2026,8 +2627,20 @@
         <f t="shared" si="4"/>
         <v>4.0644862107531571E-3</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <f t="shared" si="5"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="6"/>
+        <v>0.2601880877742947</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="7"/>
+        <v>0.4670846394984326</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>90</v>
       </c>
@@ -2049,8 +2662,20 @@
         <f t="shared" si="4"/>
         <v>3.952569169960474E-3</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <f t="shared" si="5"/>
+        <v>0.27692307692307694</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="6"/>
+        <v>0.26461538461538464</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="7"/>
+        <v>0.45846153846153848</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>89</v>
       </c>
@@ -2072,8 +2697,20 @@
         <f t="shared" si="4"/>
         <v>3.9896109459929847E-3</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <f t="shared" si="5"/>
+        <v>0.27554179566563469</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="6"/>
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="7"/>
+        <v>0.46130030959752322</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>87</v>
       </c>
@@ -2095,8 +2732,20 @@
         <f t="shared" si="4"/>
         <v>4.0460544180741867E-3</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <f t="shared" si="5"/>
+        <v>0.27187499999999998</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="6"/>
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="7"/>
+        <v>0.46562500000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>88</v>
       </c>
@@ -2118,8 +2767,20 @@
         <f t="shared" si="4"/>
         <v>4.0506883433232069E-3</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <f t="shared" si="5"/>
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="6"/>
+        <v>0.2601880877742947</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="7"/>
+        <v>0.46394984326018807</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>87</v>
       </c>
@@ -2141,8 +2802,20 @@
         <f t="shared" si="4"/>
         <v>4.0460544180741867E-3</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <f t="shared" si="5"/>
+        <v>0.27187499999999998</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="6"/>
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="7"/>
+        <v>0.46562500000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>89</v>
       </c>
@@ -2164,8 +2837,20 @@
         <f t="shared" si="4"/>
         <v>3.9946018893387315E-3</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <f t="shared" si="5"/>
+        <v>0.27639751552795033</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="6"/>
+        <v>0.2639751552795031</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="7"/>
+        <v>0.45962732919254656</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>90</v>
       </c>
@@ -2187,8 +2872,20 @@
         <f t="shared" si="4"/>
         <v>4.0116011167430137E-3</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <f t="shared" si="5"/>
+        <v>0.28037383177570091</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="6"/>
+        <v>0.25856697819314639</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="7"/>
+        <v>0.46105919003115264</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>88</v>
       </c>
@@ -2210,8 +2907,20 @@
         <f t="shared" si="4"/>
         <v>4.0506883433232069E-3</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <f t="shared" si="5"/>
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="6"/>
+        <v>0.2601880877742947</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="7"/>
+        <v>0.46394984326018807</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>87</v>
       </c>
@@ -2233,8 +2942,20 @@
         <f t="shared" si="4"/>
         <v>4.0701831582421206E-3</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <f t="shared" si="5"/>
+        <v>0.27358490566037735</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="6"/>
+        <v>0.2610062893081761</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="7"/>
+        <v>0.46540880503144655</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>86</v>
       </c>
@@ -2256,8 +2977,20 @@
         <f t="shared" si="4"/>
         <v>4.1083721963135686E-3</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <f t="shared" si="5"/>
+        <v>0.27215189873417722</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="6"/>
+        <v>0.25949367088607594</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="7"/>
+        <v>0.46835443037974683</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>90</v>
       </c>
@@ -2279,8 +3012,20 @@
         <f t="shared" si="4"/>
         <v>3.9326564708906308E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <f t="shared" si="5"/>
+        <v>0.2735562310030395</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="6"/>
+        <v>0.26139817629179329</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="7"/>
+        <v>0.46504559270516715</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>87</v>
       </c>
@@ -2302,8 +3047,20 @@
         <f t="shared" si="4"/>
         <v>4.0644862107531571E-3</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <f t="shared" si="5"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="6"/>
+        <v>0.2601880877742947</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="7"/>
+        <v>0.4670846394984326</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>89</v>
       </c>
@@ -2325,8 +3082,20 @@
         <f t="shared" si="4"/>
         <v>3.9844870636986662E-3</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <f t="shared" si="5"/>
+        <v>0.27469135802469136</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="6"/>
+        <v>0.26234567901234568</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="7"/>
+        <v>0.46296296296296297</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>98</v>
       </c>
@@ -2348,8 +3117,20 @@
         <f t="shared" si="4"/>
         <v>3.617434268572437E-3</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I62">
+        <f t="shared" si="5"/>
+        <v>0.2752808988764045</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="6"/>
+        <v>0.2640449438202247</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="7"/>
+        <v>0.4606741573033708</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>96</v>
       </c>
@@ -2371,8 +3152,20 @@
         <f t="shared" si="4"/>
         <v>3.7081394813211111E-3</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I63">
+        <f t="shared" si="5"/>
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="6"/>
+        <v>0.2614942528735632</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="7"/>
+        <v>0.46264367816091956</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>95</v>
       </c>
@@ -2394,8 +3187,20 @@
         <f t="shared" si="4"/>
         <v>3.715099715099715E-3</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I64">
+        <f t="shared" si="5"/>
+        <v>0.27220630372492838</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="6"/>
+        <v>0.26074498567335241</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="7"/>
+        <v>0.46704871060171921</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>96</v>
       </c>
@@ -2417,8 +3222,20 @@
         <f t="shared" si="4"/>
         <v>3.7036190302004984E-3</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I65">
+        <f t="shared" si="5"/>
+        <v>0.27507163323782235</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="6"/>
+        <v>0.26074498567335241</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="7"/>
+        <v>0.46418338108882523</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>98</v>
       </c>
@@ -2440,8 +3257,20 @@
         <f t="shared" si="4"/>
         <v>3.6406948783064027E-3</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I66">
+        <f t="shared" si="5"/>
+        <v>0.27762039660056659</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="6"/>
+        <v>0.26345609065155806</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="7"/>
+        <v>0.45892351274787535</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>97</v>
       </c>
@@ -2452,19 +3281,31 @@
         <v>162</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E90" si="6">A67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="E67:E90" si="10">A67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>2.2078572404060637E-3</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F90" si="7">B67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="F67:F90" si="11">B67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>2.0712887513087814E-3</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67:G90" si="8">C67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="G67:G90" si="12">C67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>3.6873492056266216E-3</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I67">
+        <f t="shared" ref="I67:I90" si="13">A67/($A67+$B67+$C67)</f>
+        <v>0.27714285714285714</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J90" si="14">B67/($A67+$B67+$C67)</f>
+        <v>0.26</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K90" si="15">C67/($A67+$B67+$C67)</f>
+        <v>0.46285714285714286</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>96</v>
       </c>
@@ -2475,19 +3316,31 @@
         <v>161</v>
       </c>
       <c r="E68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.2110645354461284E-3</v>
       </c>
       <c r="F68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0959049242249756E-3</v>
       </c>
       <c r="G68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7081394813211111E-3</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I68">
+        <f t="shared" si="13"/>
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="14"/>
+        <v>0.2614942528735632</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="15"/>
+        <v>0.46264367816091956</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>97</v>
       </c>
@@ -2498,19 +3351,31 @@
         <v>162</v>
       </c>
       <c r="E69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1986989142507422E-3</v>
       </c>
       <c r="F69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0853639186708072E-3</v>
       </c>
       <c r="G69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6720538567898997E-3</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I69">
+        <f t="shared" si="13"/>
+        <v>0.27635327635327633</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="14"/>
+        <v>0.2621082621082621</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="15"/>
+        <v>0.46153846153846156</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>98</v>
       </c>
@@ -2521,19 +3386,31 @@
         <v>163</v>
       </c>
       <c r="E70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1773423093159145E-3</v>
       </c>
       <c r="F70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0884711946499591E-3</v>
       </c>
       <c r="G70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6214979226376945E-3</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I70">
+        <f t="shared" si="13"/>
+        <v>0.27605633802816903</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="14"/>
+        <v>0.26478873239436618</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="15"/>
+        <v>0.45915492957746479</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>98</v>
       </c>
@@ -2544,19 +3421,31 @@
         <v>161</v>
       </c>
       <c r="E71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.2184995698827366E-3</v>
       </c>
       <c r="F71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1053108163172907E-3</v>
       </c>
       <c r="G71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6446778648073527E-3</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <f t="shared" si="13"/>
+        <v>0.27840909090909088</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="14"/>
+        <v>0.26420454545454547</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="15"/>
+        <v>0.45738636363636365</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>95</v>
       </c>
@@ -2567,19 +3456,31 @@
         <v>161</v>
       </c>
       <c r="E72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.2069414115132649E-3</v>
       </c>
       <c r="F72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0907866003809878E-3</v>
       </c>
       <c r="G72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7401849184593226E-3</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <f t="shared" si="13"/>
+        <v>0.27456647398843931</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="14"/>
+        <v>0.26011560693641617</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="15"/>
+        <v>0.46531791907514453</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>95</v>
       </c>
@@ -2590,19 +3491,31 @@
         <v>161</v>
       </c>
       <c r="E73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1977005112545399E-3</v>
       </c>
       <c r="F73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1051657528859276E-3</v>
       </c>
       <c r="G73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7245240243366415E-3</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <f t="shared" si="13"/>
+        <v>0.2737752161383285</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="14"/>
+        <v>0.26224783861671469</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="15"/>
+        <v>0.46397694524495675</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>97</v>
       </c>
@@ -2613,19 +3526,31 @@
         <v>163</v>
       </c>
       <c r="E74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1826200441024258E-3</v>
       </c>
       <c r="F74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0701138562620944E-3</v>
       </c>
       <c r="G74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6677017235947976E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I74">
+        <f t="shared" si="13"/>
+        <v>0.27556818181818182</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="14"/>
+        <v>0.26136363636363635</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="15"/>
+        <v>0.46306818181818182</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>97</v>
       </c>
@@ -2636,19 +3561,31 @@
         <v>165</v>
       </c>
       <c r="E75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1332746866065538E-3</v>
       </c>
       <c r="F75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0672971189795468E-3</v>
       </c>
       <c r="G75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.628766219485375E-3</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I75">
+        <f t="shared" si="13"/>
+        <v>0.27247191011235955</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="14"/>
+        <v>0.2640449438202247</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="15"/>
+        <v>0.46348314606741575</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>95</v>
       </c>
@@ -2659,19 +3596,31 @@
         <v>162</v>
       </c>
       <c r="E76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1814006888633756E-3</v>
       </c>
       <c r="F76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.08955223880597E-3</v>
       </c>
       <c r="G76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7198622273249141E-3</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I76">
+        <f t="shared" si="13"/>
+        <v>0.27298850574712646</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="14"/>
+        <v>0.2614942528735632</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="15"/>
+        <v>0.46551724137931033</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>95</v>
       </c>
@@ -2682,19 +3631,31 @@
         <v>157</v>
       </c>
       <c r="E77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.264330830651889E-3</v>
       </c>
       <c r="F77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1689905851507568E-3</v>
       </c>
       <c r="G77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7421046359194373E-3</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I77">
+        <f t="shared" si="13"/>
+        <v>0.27696793002915454</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="14"/>
+        <v>0.26530612244897961</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="15"/>
+        <v>0.45772594752186591</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>97</v>
       </c>
@@ -2705,19 +3666,31 @@
         <v>163</v>
       </c>
       <c r="E78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1645021645021645E-3</v>
       </c>
       <c r="F78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0975587985897263E-3</v>
       </c>
       <c r="G78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6372562145758022E-3</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I78">
+        <f t="shared" si="13"/>
+        <v>0.27401129943502822</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="14"/>
+        <v>0.2655367231638418</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="15"/>
+        <v>0.46045197740112992</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>96</v>
       </c>
@@ -2728,19 +3701,31 @@
         <v>160</v>
       </c>
       <c r="E79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.2369279522788704E-3</v>
       </c>
       <c r="F79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0971199552614408E-3</v>
       </c>
       <c r="G79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7282132537981173E-3</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I79">
+        <f t="shared" si="13"/>
+        <v>0.2774566473988439</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="14"/>
+        <v>0.26011560693641617</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="15"/>
+        <v>0.46242774566473988</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>97</v>
       </c>
@@ -2751,19 +3736,31 @@
         <v>162</v>
       </c>
       <c r="E80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1986989142507422E-3</v>
       </c>
       <c r="F80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0853639186708072E-3</v>
       </c>
       <c r="G80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6720538567898997E-3</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I80">
+        <f t="shared" si="13"/>
+        <v>0.27635327635327633</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="14"/>
+        <v>0.2621082621082621</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="15"/>
+        <v>0.46153846153846156</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>97</v>
       </c>
@@ -2774,19 +3771,31 @@
         <v>164</v>
       </c>
       <c r="E81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.157761267073008E-3</v>
       </c>
       <c r="F81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0687814210081415E-3</v>
       </c>
       <c r="G81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6481736886595185E-3</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I81">
+        <f t="shared" si="13"/>
+        <v>0.27401129943502822</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="14"/>
+        <v>0.26271186440677968</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="15"/>
+        <v>0.4632768361581921</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>97</v>
       </c>
@@ -2797,19 +3806,31 @@
         <v>162</v>
       </c>
       <c r="E82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1895174032775045E-3</v>
       </c>
       <c r="F82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0992280258227618E-3</v>
       </c>
       <c r="G82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6567197869170694E-3</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I82">
+        <f t="shared" si="13"/>
+        <v>0.27556818181818182</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="14"/>
+        <v>0.26420454545454547</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="15"/>
+        <v>0.46022727272727271</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>96</v>
       </c>
@@ -2820,19 +3841,31 @@
         <v>162</v>
       </c>
       <c r="E83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1855932975138877E-3</v>
       </c>
       <c r="F83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0945269101174755E-3</v>
       </c>
       <c r="G83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6881886895546853E-3</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I83">
+        <f t="shared" si="13"/>
+        <v>0.2742857142857143</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="14"/>
+        <v>0.26285714285714284</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="15"/>
+        <v>0.46285714285714286</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>94</v>
       </c>
@@ -2843,19 +3876,31 @@
         <v>160</v>
       </c>
       <c r="E84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1911421911421911E-3</v>
       </c>
       <c r="F84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1445221445221445E-3</v>
       </c>
       <c r="G84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7296037296037296E-3</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I84">
+        <f t="shared" si="13"/>
+        <v>0.27167630057803466</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="14"/>
+        <v>0.26589595375722541</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="15"/>
+        <v>0.46242774566473988</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>96</v>
       </c>
@@ -2866,19 +3911,31 @@
         <v>163</v>
       </c>
       <c r="E85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1605077193140388E-3</v>
       </c>
       <c r="F85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0929918530854753E-3</v>
       </c>
       <c r="G85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6683620650852949E-3</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I85">
+        <f t="shared" si="13"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="14"/>
+        <v>0.26420454545454547</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="15"/>
+        <v>0.46306818181818182</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>96</v>
       </c>
@@ -2889,19 +3946,31 @@
         <v>159</v>
       </c>
       <c r="E86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.2441441862639674E-3</v>
       </c>
       <c r="F86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1272616765627191E-3</v>
       </c>
       <c r="G86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7168638084996959E-3</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I86">
+        <f t="shared" si="13"/>
+        <v>0.2774566473988439</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="14"/>
+        <v>0.26300578034682082</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="15"/>
+        <v>0.45953757225433528</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>98</v>
       </c>
@@ -2912,19 +3981,31 @@
         <v>163</v>
       </c>
       <c r="E87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1864263085092143E-3</v>
       </c>
       <c r="F87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0748739458301725E-3</v>
       </c>
       <c r="G87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6366070233367544E-3</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I87">
+        <f t="shared" si="13"/>
+        <v>0.2768361581920904</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="14"/>
+        <v>0.26271186440677968</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="15"/>
+        <v>0.46045197740112992</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>99</v>
       </c>
@@ -2935,19 +4016,31 @@
         <v>165</v>
       </c>
       <c r="E88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1586498626313725E-3</v>
       </c>
       <c r="F88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0496271422964546E-3</v>
       </c>
       <c r="G88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.5977497710522875E-3</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I88">
+        <f t="shared" si="13"/>
+        <v>0.27653631284916202</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="14"/>
+        <v>0.26256983240223464</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="15"/>
+        <v>0.46089385474860334</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>95</v>
       </c>
@@ -2958,19 +4051,31 @@
         <v>162</v>
       </c>
       <c r="E89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1722726545171838E-3</v>
       </c>
       <c r="F89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1036745706903255E-3</v>
       </c>
       <c r="G89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7042965266503554E-3</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I89">
+        <f t="shared" si="13"/>
+        <v>0.27220630372492838</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="14"/>
+        <v>0.26361031518624639</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="15"/>
+        <v>0.46418338108882523</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>98</v>
       </c>
@@ -2981,16 +4086,28 @@
         <v>163</v>
       </c>
       <c r="E90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1864263085092143E-3</v>
       </c>
       <c r="F90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.0748739458301725E-3</v>
       </c>
       <c r="G90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6366070233367544E-3</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="13"/>
+        <v>0.2768361581920904</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="14"/>
+        <v>0.26271186440677968</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="15"/>
+        <v>0.46045197740112992</v>
       </c>
     </row>
   </sheetData>
